--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486989_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486989_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3166</v>
+        <v>3.9285</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8003</v>
+        <v>5.3233</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4837</v>
+        <v>-1.3947</v>
       </c>
       <c r="G2" t="n">
         <v>1.4277</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5218</v>
+        <v>0.0902</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8486</v>
+        <v>-0.3256</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3268</v>
+        <v>0.4158</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8182</v>
+        <v>3.3273</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2646</v>
+        <v>3.8922</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4464</v>
+        <v>-0.5649</v>
       </c>
       <c r="G3" t="n">
         <v>3.8068</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5942</v>
+        <v>-0.0852</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7827</v>
+        <v>-0.1551</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1885</v>
+        <v>0.0699</v>
       </c>
       <c r="V3" t="n">
         <v>1.6591</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4461</v>
+        <v>1.7577</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6279</v>
+        <v>1.844</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1818</v>
+        <v>-0.0863</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2974</v>
+        <v>0.9382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8208</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5234</v>
+        <v>0.3157</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5068</v>
+        <v>1.5031</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4278</v>
+        <v>0.7008</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0789</v>
+        <v>0.8023</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2094</v>
+        <v>-0.5649</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6071</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.4866</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2588</v>
+        <v>0.8214</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6396</v>
+        <v>-0.0019</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4333</v>
+        <v>0.3409</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2062</v>
+        <v>-0.3428</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3566</v>
+        <v>1.121</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7394</v>
+        <v>0.8799</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3827</v>
+        <v>0.2411</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9382</v>
+        <v>1.3401</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6225000000000001</v>
+        <v>2.0792</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3157</v>
+        <v>-0.7391</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5031</v>
+        <v>2.026</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7008</v>
+        <v>1.9076</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8023</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5649</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.1716</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4866</v>
+        <v>-0.8575</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
         <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.403</v>
+        <v>0.3148</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2362</v>
+        <v>-0.2713</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6392</v>
+        <v>0.5861</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8369</v>
+        <v>0.2502</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5661</v>
+        <v>0.3727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2707</v>
+        <v>-0.1225</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3401</v>
+        <v>0.2974</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0792</v>
+        <v>0.8208</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7391</v>
+        <v>-0.5234</v>
       </c>
       <c r="J6" t="n">
-        <v>2.026</v>
+        <v>1.5068</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9076</v>
+        <v>1.4278</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1184</v>
+        <v>0.0789</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-1.2094</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1716</v>
+        <v>-0.6071</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8575</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0307</v>
+        <v>0.4436</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5851</v>
+        <v>0.1781</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6158</v>
+        <v>0.2655</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6982</v>
+        <v>1.7679</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1786</v>
+        <v>1.7679</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1264</v>
+        <v>0.1857</v>
       </c>
       <c r="E7" t="n">
         <v>2.2815</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1551</v>
+        <v>-2.0958</v>
       </c>
       <c r="G7" t="n">
         <v>2.1795</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2317</v>
+        <v>-0.1724</v>
       </c>
       <c r="T7" t="n">
         <v>0.0464</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.278</v>
+        <v>-0.2188</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5893</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0222</v>
+        <v>-1.4092</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3854</v>
+        <v>1.1762</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4076</v>
+        <v>-2.5854</v>
       </c>
       <c r="G8" t="n">
         <v>0.2638</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6873</v>
+        <v>0.3003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2362</v>
+        <v>0.027</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4511</v>
+        <v>0.2732</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7679</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7991</v>
+        <v>-2.1129</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.2351</v>
       </c>
       <c r="F9" t="n">
         <v>-2.3479</v>
@@ -1156,10 +1156,10 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>0.616</v>
+        <v>0.3022</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3485</v>
+        <v>0.0347</v>
       </c>
       <c r="U9" t="n">
         <v>0.2675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5794</v>
+        <v>-5.5481</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9291</v>
+        <v>-4.7199</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6503</v>
+        <v>-0.8282</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0192</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0559</v>
+        <v>0.0872</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3952</v>
+        <v>-0.186</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4511</v>
+        <v>0.2732</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.500100000000001</v>
+        <v>1.500200000000001</v>
       </c>
       <c r="E11" t="n">
         <v>11.285</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.784799999999999</v>
+        <v>-9.784600000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>6.578999999999999</v>
+        <v>6.579000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>1.816</v>
@@ -1315,10 +1315,10 @@
         <v>1.2788</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3109999999999999</v>
+        <v>-0.3109</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5898</v>
+        <v>1.5896</v>
       </c>
       <c r="V11" t="n">
         <v>0.8295999999999994</v>
@@ -1327,7 +1327,7 @@
         <v>9.691700000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.862200000000001</v>
+        <v>-8.8622</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4911</v>
+        <v>5.1955</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1447</v>
+        <v>3.3539</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3464</v>
+        <v>1.8416</v>
       </c>
       <c r="G12" t="n">
         <v>3.2575</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3824</v>
+        <v>-0.678</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9222</v>
+        <v>-0.713</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4602</v>
+        <v>0.035</v>
       </c>
       <c r="V12" t="n">
         <v>1.1786</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7429</v>
+        <v>1.0437</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5059</v>
+        <v>4.1921</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.763</v>
+        <v>-3.1484</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7010999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0333</v>
+        <v>0.3341</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3408</v>
+        <v>0.0269</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6925</v>
+        <v>0.3072</v>
       </c>
       <c r="V13" t="n">
         <v>0.5893</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7289</v>
+        <v>0.2183</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3695</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6407</v>
+        <v>-0.6381</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.0056</v>
+        <v>0.1302</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.5554</v>
+        <v>2.3778</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5498</v>
+        <v>-2.2476</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7611</v>
+        <v>2.2708</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.2249</v>
+        <v>2.732</v>
       </c>
       <c r="L14" t="n">
-        <v>2.986</v>
+        <v>-0.4613</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7667</v>
+        <v>-2.1405</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3305</v>
+        <v>-0.3542</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.4362</v>
+        <v>-1.7863</v>
       </c>
       <c r="P14" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.4374</v>
+      </c>
+      <c r="R14" t="n">
         <v>2.0534</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-0.4107</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.4641</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.0917</v>
+        <v>-0.0475</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8405</v>
+        <v>0.0231</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2512</v>
+        <v>-0.0706</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5893</v>
+        <v>-0.4805</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5893</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6119</v>
+        <v>-0.0626</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3136</v>
+        <v>1.6373</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2983</v>
+        <v>-1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3261</v>
+        <v>-3.0056</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1395</v>
+        <v>-3.5554</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4655</v>
+        <v>0.5498</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6702</v>
+        <v>0.7611</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4214</v>
+        <v>-2.2249</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0916</v>
+        <v>2.986</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3441</v>
+        <v>-3.7667</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2819</v>
+        <v>-1.3305</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6261</v>
+        <v>-2.4362</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.3002</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6701</v>
+        <v>0.1083</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0613</v>
+        <v>0.1919</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. MENDES KOVACS</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3114</v>
+        <v>-0.1447</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1849</v>
+        <v>-0.5232</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1264</v>
+        <v>0.3785</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0691</v>
+        <v>0.3261</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0929</v>
+        <v>-0.1395</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0238</v>
+        <v>0.4655</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5397</v>
+        <v>0.6702</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4477</v>
+        <v>-0.4214</v>
       </c>
       <c r="L16" t="n">
-        <v>0.092</v>
+        <v>1.0916</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5294</v>
+        <v>-0.3441</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6452</v>
+        <v>0.2819</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1157</v>
+        <v>-0.6261</v>
       </c>
       <c r="P16" t="n">
         <v>-0.2053</v>
@@ -1702,28 +1702,28 @@
         <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2437</v>
+        <v>-0.0252</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3021</v>
+        <v>-0.1667</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0584</v>
+        <v>0.1415</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>K. MENDES KOVACS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3832</v>
+        <v>-0.4107</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5426</v>
+        <v>-0.3941</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9258</v>
+        <v>-0.0166</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1302</v>
+        <v>1.0691</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3778</v>
+        <v>1.0929</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2476</v>
+        <v>-0.0238</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2708</v>
+        <v>0.5397</v>
       </c>
       <c r="K17" t="n">
-        <v>2.732</v>
+        <v>0.4477</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4613</v>
+        <v>0.092</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1405</v>
+        <v>0.5294</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3542</v>
+        <v>0.6452</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7863</v>
+        <v>-0.1157</v>
       </c>
       <c r="P17" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.4374</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.649</v>
+        <v>0.1443</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2907</v>
+        <v>0.0929</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3582</v>
+        <v>0.0514</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7043</v>
+        <v>-0.5404</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3458</v>
+        <v>2.4504</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0501</v>
+        <v>-2.9908</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5411</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.2266</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0272</v>
+        <v>0.0774</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1492</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4579</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1632</v>
+        <v>-0.9243</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.4687</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4853</v>
+        <v>-0.4556</v>
       </c>
       <c r="G19" t="n">
         <v>-0.904</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2592</v>
+        <v>-0.0203</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.2092</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2592</v>
+        <v>-0.2295</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.595</v>
+        <v>-1.3701</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8117</v>
+        <v>-1.4979</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2167</v>
+        <v>0.1278</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4117</v>
@@ -2014,13 +2014,13 @@
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.594</v>
+        <v>-0.3691</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.054</v>
+        <v>-0.7401</v>
       </c>
       <c r="U20" t="n">
-        <v>0.46</v>
+        <v>0.371</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0729</v>
+        <v>-1.5185</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4058</v>
+        <v>2.138</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4787</v>
+        <v>-3.6565</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4232</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6765</v>
+        <v>-0.1221</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9881</v>
+        <v>-0.2559</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3116</v>
+        <v>0.1338</v>
       </c>
       <c r="V21" t="n">
         <v>0.5893</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8452</v>
+        <v>-2.289</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1687</v>
+        <v>-1.9595</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6765</v>
+        <v>-0.3295</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3752</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8807</v>
+        <v>-0.3245</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4611</v>
+        <v>-0.2519</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4196</v>
+        <v>-0.0726</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5004</v>
+        <v>-0.8027999999999995</v>
       </c>
       <c r="E23" t="n">
         <v>9.784699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.2851</v>
+        <v>-10.5876</v>
       </c>
       <c r="G23" t="n">
         <v>-6.578999999999999</v>
@@ -2233,13 +2233,13 @@
         <v>-17.3049</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.242699999999999</v>
+        <v>-5.2427</v>
       </c>
       <c r="O23" t="n">
         <v>-12.0621</v>
       </c>
       <c r="P23" t="n">
-        <v>7.187099999999999</v>
+        <v>7.187100000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-8.2136</v>
@@ -2248,13 +2248,13 @@
         <v>15.4007</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.279</v>
+        <v>-0.5814999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>-1.5898</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3109</v>
+        <v>1.0083</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8296</v>
@@ -2263,7 +2263,7 @@
         <v>8.862200000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.691800000000001</v>
+        <v>-9.691799999999999</v>
       </c>
     </row>
   </sheetData>
